--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7578,0.0910,0.0485,0.0364</t>
-  </si>
-  <si>
-    <t>0.8165,0.0307,0.0136,0.0778</t>
-  </si>
-  <si>
-    <t>0.7081,0.0972,0.0560,0.0750</t>
-  </si>
-  <si>
-    <t>0.7083,0.0691,0.0135,0.0677</t>
-  </si>
-  <si>
-    <t>0.7851,0.1173,0.0073,0.0101</t>
-  </si>
-  <si>
-    <t>0.6874,0.1403,0.0196,0.0325</t>
-  </si>
-  <si>
-    <t>0.6841,0.1150,0.0132,0.0307</t>
-  </si>
-  <si>
-    <t>0.6719,0.1853,0.0114,0.0149</t>
-  </si>
-  <si>
-    <t>0.8062,0.0551,0.0117,0.0393</t>
-  </si>
-  <si>
-    <t>0.6607,0.1307,0.0220,0.0463</t>
-  </si>
-  <si>
-    <t>0.8620,0.0565,0.0044,0.0108</t>
-  </si>
-  <si>
-    <t>0.8725,0.0494,0.0070,0.0131</t>
-  </si>
-  <si>
-    <t>0.7931,0.0814,0.0278,0.0284</t>
-  </si>
-  <si>
-    <t>0.4324,0.4102,0.2449,0.0334</t>
-  </si>
-  <si>
-    <t>0.7557,0.0950,0.0979,0.0341</t>
-  </si>
-  <si>
-    <t>0.8306,0.0638,0.0417,0.0306</t>
-  </si>
-  <si>
-    <t>0.7715,0.1424,0.0454,0.0066</t>
-  </si>
-  <si>
-    <t>0.2990,0.6878,0.0367,0.0055</t>
-  </si>
-  <si>
-    <t>0.2836,0.6889,0.1081,0.0090</t>
-  </si>
-  <si>
-    <t>0.6958,0.2379,0.0354,0.0182</t>
-  </si>
-  <si>
-    <t>0.0450,0.9379,0.0308,0.0068</t>
-  </si>
-  <si>
-    <t>0.2033,0.7724,0.0093,0.0055</t>
-  </si>
-  <si>
-    <t>0.8363,0.0248,0.0595,0.0590</t>
-  </si>
-  <si>
-    <t>0.8785,0.0200,0.0106,0.0319</t>
-  </si>
-  <si>
-    <t>0.6971,0.1208,0.1908,0.0157</t>
-  </si>
-  <si>
-    <t>0.7420,0.0482,0.1374,0.0506</t>
-  </si>
-  <si>
-    <t>0.8467,0.0150,0.0724,0.0464</t>
-  </si>
-  <si>
-    <t>0.8658,0.0188,0.1293,0.0078</t>
-  </si>
-  <si>
-    <t>0.5098,0.3278,0.2200,0.0145</t>
-  </si>
-  <si>
-    <t>0.5397,0.4788,0.0295,0.0063</t>
-  </si>
-  <si>
-    <t>0.8429,0.0780,0.0131,0.0150</t>
-  </si>
-  <si>
-    <t>0.0206,0.7980,0.9117,0.0028</t>
-  </si>
-  <si>
-    <t>0.7056,0.1719,0.0423,0.0325</t>
-  </si>
-  <si>
-    <t>0.7285,0.1237,0.0432,0.0458</t>
-  </si>
-  <si>
-    <t>0.7160,0.1392,0.0332,0.0281</t>
-  </si>
-  <si>
-    <t>0.7249,0.0875,0.0066,0.0270</t>
-  </si>
-  <si>
-    <t>0.7302,0.1160,0.0189,0.0253</t>
-  </si>
-  <si>
-    <t>0.4394,0.4036,0.1208,0.0178</t>
-  </si>
-  <si>
-    <t>0.8367,0.0092,0.1849,0.0076</t>
-  </si>
-  <si>
-    <t>0.8068,0.0363,0.1329,0.0107</t>
-  </si>
-  <si>
-    <t>0.9143,0.0158,0.0228,0.0181</t>
-  </si>
-  <si>
-    <t>0.7161,0.0143,0.3355,0.0076</t>
-  </si>
-  <si>
-    <t>0.3740,0.4817,0.1097,0.0243</t>
-  </si>
-  <si>
-    <t>0.7714,0.0591,0.1615,0.0171</t>
-  </si>
-  <si>
-    <t>0.7891,0.0767,0.0054,0.0170</t>
-  </si>
-  <si>
-    <t>0.6505,0.3810,0.0211,0.0032</t>
-  </si>
-  <si>
-    <t>0.2115,0.7892,0.0444,0.0065</t>
-  </si>
-  <si>
-    <t>0.3988,0.5390,0.0323,0.0116</t>
-  </si>
-  <si>
-    <t>0.0335,0.4213,0.9363,0.0052</t>
-  </si>
-  <si>
-    <t>0.2246,0.5097,0.5319,0.0056</t>
-  </si>
-  <si>
-    <t>0.7727,0.0321,0.1776,0.0210</t>
-  </si>
-  <si>
-    <t>0.6583,0.0184,0.4482,0.0050</t>
-  </si>
-  <si>
-    <t>0.0417,0.4729,0.9332,0.0012</t>
-  </si>
-  <si>
-    <t>0.3642,0.3162,0.4687,0.0060</t>
-  </si>
-  <si>
-    <t>0.8140,0.0308,0.0054,0.0404</t>
-  </si>
-  <si>
-    <t>0.6382,0.1505,0.0884,0.1104</t>
-  </si>
-  <si>
-    <t>0.8726,0.0392,0.0101,0.0235</t>
-  </si>
-  <si>
-    <t>0.2754,0.4892,0.4706,0.0259</t>
-  </si>
-  <si>
-    <t>0.6528,0.2385,0.0344,0.0167</t>
-  </si>
-  <si>
-    <t>0.5648,0.2567,0.0448,0.0366</t>
-  </si>
-  <si>
-    <t>0.7706,0.0864,0.0200,0.0293</t>
-  </si>
-  <si>
-    <t>0.2436,0.5326,0.4184,0.0108</t>
-  </si>
-  <si>
-    <t>0.2243,0.2610,0.6924,0.0184</t>
-  </si>
-  <si>
-    <t>0.3260,0.2775,0.5000,0.0224</t>
-  </si>
-  <si>
-    <t>0.0103,0.9308,0.8299,0.0008</t>
-  </si>
-  <si>
-    <t>0.0482,0.0983,0.9576,0.0011</t>
-  </si>
-  <si>
-    <t>0.1635,0.8338,0.0658,0.0025</t>
-  </si>
-  <si>
-    <t>0.0059,0.9921,0.0353,0.0006</t>
-  </si>
-  <si>
-    <t>0.8760,0.0496,0.0074,0.0151</t>
-  </si>
-  <si>
-    <t>0.6497,0.1914,0.0841,0.0491</t>
-  </si>
-  <si>
-    <t>0.0068,0.8292,0.9523,0.0026</t>
-  </si>
-  <si>
-    <t>0.2325,0.4699,0.5673,0.0060</t>
-  </si>
-  <si>
-    <t>0.7558,0.1026,0.1149,0.0161</t>
-  </si>
-  <si>
-    <t>0.0031,0.9861,0.6359,0.0007</t>
-  </si>
-  <si>
-    <t>0.0005,0.9720,0.9808,0.0002</t>
-  </si>
-  <si>
-    <t>0.7418,0.0454,0.0298,0.1079</t>
-  </si>
-  <si>
-    <t>0.7155,0.0350,0.0164,0.1568</t>
-  </si>
-  <si>
-    <t>0.8603,0.0213,0.0029,0.0386</t>
-  </si>
-  <si>
-    <t>0.8483,0.0338,0.0183,0.0586</t>
-  </si>
-  <si>
-    <t>0.6411,0.0556,0.0388,0.1822</t>
-  </si>
-  <si>
-    <t>0.8541,0.0073,0.0021,0.0994</t>
-  </si>
-  <si>
-    <t>0.0522,0.7409,0.7191,0.0183</t>
-  </si>
-  <si>
-    <t>0.0288,0.7041,0.8906,0.0048</t>
-  </si>
-  <si>
-    <t>0.7150,0.1463,0.1172,0.0095</t>
-  </si>
-  <si>
-    <t>0.2604,0.2212,0.6801,0.0157</t>
-  </si>
-  <si>
-    <t>0.5034,0.2890,0.1841,0.0094</t>
-  </si>
-  <si>
-    <t>0.4468,0.3945,0.1818,0.0164</t>
-  </si>
-  <si>
-    <t>0.7271,0.1779,0.0287,0.0149</t>
-  </si>
-  <si>
-    <t>0.8278,0.0586,0.0083,0.0207</t>
-  </si>
-  <si>
-    <t>0.6976,0.1936,0.0170,0.0156</t>
-  </si>
-  <si>
-    <t>0.6635,0.1622,0.0127,0.0169</t>
-  </si>
-  <si>
-    <t>0.5722,0.0714,0.0133,0.1054</t>
-  </si>
-  <si>
-    <t>0.6376,0.1388,0.0316,0.0619</t>
-  </si>
-  <si>
-    <t>0.5509,0.4057,0.0285,0.0077</t>
-  </si>
-  <si>
-    <t>0.6540,0.1104,0.0463,0.0950</t>
-  </si>
-  <si>
-    <t>0.8058,0.0545,0.0136,0.0359</t>
-  </si>
-  <si>
-    <t>0.8263,0.1024,0.0040,0.0061</t>
-  </si>
-  <si>
-    <t>0.7027,0.1040,0.0099,0.0272</t>
-  </si>
-  <si>
-    <t>0.7432,0.0674,0.0089,0.0292</t>
-  </si>
-  <si>
-    <t>0.7935,0.1039,0.0078,0.0111</t>
-  </si>
-  <si>
-    <t>0.8452,0.0605,0.0082,0.0179</t>
-  </si>
-  <si>
-    <t>0.8377,0.0825,0.0060,0.0097</t>
-  </si>
-  <si>
-    <t>0.6416,0.1191,0.0064,0.0288</t>
-  </si>
-  <si>
-    <t>0.2191,0.0638,0.8768,0.0020</t>
-  </si>
-  <si>
-    <t>0.6383,0.1706,0.1566,0.0666</t>
-  </si>
-  <si>
-    <t>0.9091,0.0232,0.0410,0.0108</t>
-  </si>
-  <si>
-    <t>0.7857,0.0591,0.0954,0.0138</t>
-  </si>
-  <si>
-    <t>0.1954,0.6990,0.0351,0.0171</t>
-  </si>
-  <si>
-    <t>0.1493,0.8947,0.0097,0.0016</t>
-  </si>
-  <si>
-    <t>0.5353,0.2910,0.0667,0.0416</t>
-  </si>
-  <si>
-    <t>0.5793,0.2868,0.0139,0.0145</t>
-  </si>
-  <si>
-    <t>0.5078,0.3791,0.0762,0.0231</t>
-  </si>
-  <si>
-    <t>0.0265,0.9451,0.0624,0.0120</t>
-  </si>
-  <si>
-    <t>0.5663,0.3394,0.0104,0.0114</t>
-  </si>
-  <si>
-    <t>0.9350,0.0163,0.0032,0.0101</t>
-  </si>
-  <si>
-    <t>0.7835,0.0839,0.0700,0.0294</t>
-  </si>
-  <si>
-    <t>0.8682,0.0363,0.0136,0.0258</t>
-  </si>
-  <si>
-    <t>0.8370,0.0679,0.0530,0.0216</t>
-  </si>
-  <si>
-    <t>0.5947,0.1127,0.0621,0.1542</t>
-  </si>
-  <si>
-    <t>0.3413,0.5191,0.0507,0.0194</t>
-  </si>
-  <si>
-    <t>0.6340,0.2634,0.0221,0.0163</t>
-  </si>
-  <si>
-    <t>0.7824,0.0729,0.0173,0.0256</t>
-  </si>
-  <si>
-    <t>0.0215,0.9429,0.5526,0.0163</t>
-  </si>
-  <si>
-    <t>0.8381,0.0960,0.0053,0.0060</t>
-  </si>
-  <si>
-    <t>0.7588,0.1366,0.0076,0.0090</t>
-  </si>
-  <si>
-    <t>0.6546,0.2466,0.0117,0.0106</t>
-  </si>
-  <si>
-    <t>0.8982,0.0321,0.0051,0.0186</t>
-  </si>
-  <si>
-    <t>0.7915,0.0623,0.0150,0.0338</t>
-  </si>
-  <si>
-    <t>0.7361,0.1410,0.0226,0.0249</t>
-  </si>
-  <si>
-    <t>0.6720,0.1979,0.0243,0.0183</t>
-  </si>
-  <si>
-    <t>0.8393,0.0239,0.0050,0.0387</t>
-  </si>
-  <si>
-    <t>0.8649,0.0702,0.0071,0.0077</t>
-  </si>
-  <si>
-    <t>0.5638,0.2433,0.0262,0.0237</t>
-  </si>
-  <si>
-    <t>0.7349,0.0419,0.0101,0.0714</t>
-  </si>
-  <si>
-    <t>0.4708,0.0389,0.6017,0.0039</t>
-  </si>
-  <si>
-    <t>0.6526,0.0837,0.2763,0.0059</t>
-  </si>
-  <si>
-    <t>0.6447,0.0580,0.3283,0.0199</t>
-  </si>
-  <si>
-    <t>0.7988,0.0190,0.1464,0.0230</t>
-  </si>
-  <si>
-    <t>0.7899,0.1137,0.0230,0.0193</t>
-  </si>
-  <si>
-    <t>0.7439,0.1188,0.0392,0.0295</t>
-  </si>
-  <si>
-    <t>0.8188,0.0553,0.0255,0.0299</t>
-  </si>
-  <si>
-    <t>0.7581,0.0953,0.0244,0.0359</t>
-  </si>
-  <si>
-    <t>0.7965,0.0218,0.0064,0.0759</t>
-  </si>
-  <si>
-    <t>0.7956,0.0453,0.0154,0.0622</t>
-  </si>
-  <si>
-    <t>0.8538,0.0229,0.0184,0.0676</t>
-  </si>
-  <si>
-    <t>0.7533,0.0710,0.0797,0.0739</t>
-  </si>
-  <si>
-    <t>0.0042,0.9672,0.7599,0.0063</t>
-  </si>
-  <si>
-    <t>0.8786,0.0351,0.0065,0.0209</t>
-  </si>
-  <si>
-    <t>0.5402,0.1503,0.0268,0.0898</t>
-  </si>
-  <si>
-    <t>0.7581,0.1274,0.0210,0.0227</t>
-  </si>
-  <si>
-    <t>0.8283,0.0954,0.0084,0.0114</t>
-  </si>
-  <si>
-    <t>0.6146,0.1200,0.0125,0.0474</t>
-  </si>
-  <si>
-    <t>0.9313,0.0176,0.0014,0.0083</t>
-  </si>
-  <si>
-    <t>0.7832,0.1077,0.0136,0.0204</t>
-  </si>
-  <si>
-    <t>0.0746,0.5608,0.7342,0.0390</t>
-  </si>
-  <si>
-    <t>0.8883,0.0333,0.0112,0.0188</t>
-  </si>
-  <si>
-    <t>0.8600,0.0201,0.0046,0.0307</t>
-  </si>
-  <si>
-    <t>0.6548,0.1854,0.0221,0.0356</t>
-  </si>
-  <si>
-    <t>0.7171,0.2041,0.0168,0.0105</t>
-  </si>
-  <si>
-    <t>0.6855,0.2485,0.0287,0.0122</t>
-  </si>
-  <si>
-    <t>0.6751,0.0586,0.0474,0.1382</t>
-  </si>
-  <si>
-    <t>0.9084,0.0409,0.0036,0.0064</t>
-  </si>
-  <si>
-    <t>0.7040,0.2953,0.0099,0.0054</t>
-  </si>
-  <si>
-    <t>0.8812,0.0695,0.0066,0.0071</t>
-  </si>
-  <si>
-    <t>0.8012,0.0599,0.0154,0.0366</t>
-  </si>
-  <si>
-    <t>0.6796,0.1726,0.0109,0.0158</t>
-  </si>
-  <si>
-    <t>0.6939,0.1164,0.0134,0.0300</t>
-  </si>
-  <si>
-    <t>0.8813,0.0417,0.0086,0.0144</t>
-  </si>
-  <si>
-    <t>0.8525,0.0380,0.0031,0.0177</t>
-  </si>
-  <si>
-    <t>0.8327,0.0492,0.0051,0.0199</t>
-  </si>
-  <si>
-    <t>0.6796,0.1056,0.0184,0.0488</t>
-  </si>
-  <si>
-    <t>0.5523,0.3971,0.0297,0.0101</t>
-  </si>
-  <si>
-    <t>0.8165,0.0792,0.0113,0.0179</t>
-  </si>
-  <si>
-    <t>0.6546,0.3586,0.0216,0.0057</t>
-  </si>
-  <si>
-    <t>0.8482,0.0383,0.0082,0.0283</t>
-  </si>
-  <si>
-    <t>0.7674,0.0404,0.0061,0.0542</t>
-  </si>
-  <si>
-    <t>0.8753,0.0195,0.0035,0.0315</t>
-  </si>
-  <si>
-    <t>0.8329,0.0380,0.0051,0.0300</t>
-  </si>
-  <si>
-    <t>0.7565,0.1251,0.0140,0.0169</t>
-  </si>
-  <si>
-    <t>0.0297,0.6553,0.9023,0.0090</t>
-  </si>
-  <si>
-    <t>0.6930,0.2015,0.0323,0.0186</t>
-  </si>
-  <si>
-    <t>0.4668,0.0337,0.6980,0.0032</t>
-  </si>
-  <si>
-    <t>0.1143,0.5362,0.7817,0.0073</t>
-  </si>
-  <si>
-    <t>0.5707,0.0601,0.3319,0.0534</t>
-  </si>
-  <si>
-    <t>0.4979,0.2760,0.2572,0.0194</t>
-  </si>
-  <si>
-    <t>0.3943,0.1990,0.5191,0.0338</t>
-  </si>
-  <si>
-    <t>0.2723,0.0717,0.7736,0.0023</t>
-  </si>
-  <si>
-    <t>0.4119,0.2768,0.3662,0.0600</t>
-  </si>
-  <si>
-    <t>0.8127,0.0825,0.0290,0.0238</t>
-  </si>
-  <si>
-    <t>0.7775,0.0723,0.1012,0.0672</t>
-  </si>
-  <si>
-    <t>0.7155,0.1479,0.1223,0.0186</t>
-  </si>
-  <si>
-    <t>0.8411,0.1014,0.0221,0.0081</t>
-  </si>
-  <si>
-    <t>0.5673,0.2223,0.1296,0.0625</t>
-  </si>
-  <si>
-    <t>0.7990,0.1436,0.0340,0.0092</t>
-  </si>
-  <si>
-    <t>0.8663,0.0266,0.0153,0.0487</t>
-  </si>
-  <si>
-    <t>0.8430,0.0369,0.0170,0.0308</t>
-  </si>
-  <si>
-    <t>0.2592,0.7207,0.0483,0.0107</t>
-  </si>
-  <si>
-    <t>0.5944,0.2067,0.0213,0.0339</t>
-  </si>
-  <si>
-    <t>0.7188,0.0997,0.0203,0.0356</t>
-  </si>
-  <si>
-    <t>0.4944,0.4040,0.0332,0.0138</t>
-  </si>
-  <si>
-    <t>0.6312,0.1593,0.0259,0.0459</t>
-  </si>
-  <si>
-    <t>0.8543,0.0390,0.0097,0.0272</t>
-  </si>
-  <si>
-    <t>0.8716,0.0259,0.0155,0.0387</t>
-  </si>
-  <si>
-    <t>0.8396,0.0353,0.0470,0.0414</t>
-  </si>
-  <si>
-    <t>0.8514,0.0384,0.0594,0.0251</t>
-  </si>
-  <si>
-    <t>0.9220,0.0321,0.0080,0.0062</t>
-  </si>
-  <si>
-    <t>0.8951,0.0309,0.0434,0.0145</t>
-  </si>
-  <si>
-    <t>0.5187,0.1296,0.3814,0.0296</t>
-  </si>
-  <si>
-    <t>0.7580,0.1124,0.1364,0.0075</t>
-  </si>
-  <si>
-    <t>0.8073,0.0221,0.1361,0.0265</t>
-  </si>
-  <si>
-    <t>0.4295,0.2710,0.3371,0.0019</t>
-  </si>
-  <si>
-    <t>0.8232,0.0629,0.0106,0.0187</t>
-  </si>
-  <si>
-    <t>0.7074,0.1955,0.0102,0.0119</t>
-  </si>
-  <si>
-    <t>0.3599,0.4891,0.0860,0.0322</t>
-  </si>
-  <si>
-    <t>0.6566,0.2227,0.0356,0.0210</t>
-  </si>
-  <si>
-    <t>0.6478,0.1844,0.0501,0.0410</t>
-  </si>
-  <si>
-    <t>0.7219,0.0793,0.0136,0.0426</t>
-  </si>
-  <si>
-    <t>0.7795,0.1085,0.0107,0.0169</t>
-  </si>
-  <si>
-    <t>0.4976,0.3358,0.0173,0.0172</t>
-  </si>
-  <si>
-    <t>0.6962,0.1239,0.1326,0.0513</t>
-  </si>
-  <si>
-    <t>0.7789,0.1051,0.0387,0.0252</t>
-  </si>
-  <si>
-    <t>0.7882,0.0460,0.0106,0.0344</t>
-  </si>
-  <si>
-    <t>0.4558,0.0565,0.5921,0.0113</t>
-  </si>
-  <si>
-    <t>0.4168,0.1030,0.4648,0.0753</t>
-  </si>
-  <si>
-    <t>0.9067,0.0337,0.0246,0.0081</t>
-  </si>
-  <si>
-    <t>0.0294,0.2200,0.9604,0.0022</t>
-  </si>
-  <si>
-    <t>0.8328,0.0465,0.0872,0.0187</t>
-  </si>
-  <si>
-    <t>0.2208,0.2777,0.6495,0.0116</t>
-  </si>
-  <si>
-    <t>0.6283,0.1342,0.2093,0.0400</t>
-  </si>
-  <si>
-    <t>0.7136,0.0999,0.0930,0.0630</t>
-  </si>
-  <si>
-    <t>0.8935,0.0169,0.0122,0.0364</t>
-  </si>
-  <si>
-    <t>0.8591,0.0394,0.0323,0.0260</t>
-  </si>
-  <si>
-    <t>0.8882,0.0324,0.0249,0.0236</t>
-  </si>
-  <si>
-    <t>0.6730,0.1589,0.0303,0.0348</t>
-  </si>
-  <si>
-    <t>0.4409,0.4122,0.0387,0.0186</t>
-  </si>
-  <si>
-    <t>0.8350,0.0569,0.0132,0.0276</t>
-  </si>
-  <si>
-    <t>0.6855,0.1150,0.0247,0.0471</t>
-  </si>
-  <si>
-    <t>0.7338,0.2002,0.0079,0.0076</t>
-  </si>
-  <si>
-    <t>0.8594,0.0534,0.0076,0.0161</t>
-  </si>
-  <si>
-    <t>0.7694,0.0878,0.0130,0.0220</t>
-  </si>
-  <si>
-    <t>0.7580,0.1238,0.0111,0.0152</t>
-  </si>
-  <si>
-    <t>0.4993,0.3293,0.2298,0.0095</t>
-  </si>
-  <si>
-    <t>0.4108,0.1690,0.5345,0.0118</t>
-  </si>
-  <si>
-    <t>0.1227,0.1398,0.8540,0.0057</t>
-  </si>
-  <si>
-    <t>0.6658,0.1350,0.1536,0.0097</t>
-  </si>
-  <si>
-    <t>0.5574,0.1717,0.3051,0.0376</t>
-  </si>
-  <si>
-    <t>0.8069,0.0505,0.0756,0.0248</t>
-  </si>
-  <si>
-    <t>0.7145,0.0626,0.2107,0.0170</t>
-  </si>
-  <si>
-    <t>0.7667,0.0318,0.1691,0.0357</t>
-  </si>
-  <si>
-    <t>0.9090,0.0314,0.0092,0.0201</t>
-  </si>
-  <si>
-    <t>0.8810,0.0236,0.0154,0.0351</t>
-  </si>
-  <si>
-    <t>0.7975,0.0400,0.0114,0.0734</t>
-  </si>
-  <si>
-    <t>0.7639,0.0210,0.0089,0.1166</t>
-  </si>
-  <si>
-    <t>0.9236,0.0088,0.0056,0.0333</t>
-  </si>
-  <si>
-    <t>0.6519,0.1530,0.0824,0.0655</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9286,0.0086,0.0162,0.0382</t>
+  </si>
+  <si>
+    <t>0.0299,0.0013,0.0016,0.9903</t>
+  </si>
+  <si>
+    <t>0.6922,0.0009,0.0076,0.4148</t>
+  </si>
+  <si>
+    <t>0.0444,0.0223,0.0015,0.9645</t>
+  </si>
+  <si>
+    <t>0.9942,0.0013,0.0003,0.0018</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9933,0.0024,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9957,0.0004,0.0003,0.0020</t>
+  </si>
+  <si>
+    <t>0.9863,0.0057,0.0018,0.0032</t>
+  </si>
+  <si>
+    <t>0.9850,0.0134,0.0022,0.0007</t>
+  </si>
+  <si>
+    <t>0.9924,0.0037,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.8406,0.0066,0.2120,0.0061</t>
+  </si>
+  <si>
+    <t>0.0985,0.0124,0.9296,0.0028</t>
+  </si>
+  <si>
+    <t>0.3184,0.0067,0.8362,0.0009</t>
+  </si>
+  <si>
+    <t>0.0639,0.0044,0.9606,0.0012</t>
+  </si>
+  <si>
+    <t>0.9070,0.0019,0.1467,0.0027</t>
+  </si>
+  <si>
+    <t>0.0002,0.9992,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0024,0.9954,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.0479,0.9449,0.0024,0.0035</t>
+  </si>
+  <si>
+    <t>0.0124,0.9761,0.0092,0.0018</t>
+  </si>
+  <si>
+    <t>0.0004,0.9983,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.4807,0.0109,0.6305,0.0127</t>
+  </si>
+  <si>
+    <t>0.6960,0.0063,0.3584,0.0138</t>
+  </si>
+  <si>
+    <t>0.0017,0.0014,0.9977,0.0003</t>
+  </si>
+  <si>
+    <t>0.1028,0.0243,0.8833,0.0057</t>
+  </si>
+  <si>
+    <t>0.0545,0.0203,0.9310,0.0145</t>
+  </si>
+  <si>
+    <t>0.4270,0.0036,0.7784,0.0012</t>
+  </si>
+  <si>
+    <t>0.0083,0.0013,0.9879,0.0043</t>
+  </si>
+  <si>
+    <t>0.1883,0.7883,0.0283,0.0032</t>
+  </si>
+  <si>
+    <t>0.6002,0.0756,0.4052,0.0123</t>
+  </si>
+  <si>
+    <t>0.0003,0.0067,0.9983,0.0011</t>
+  </si>
+  <si>
+    <t>0.0048,0.9810,0.0307,0.0003</t>
+  </si>
+  <si>
+    <t>0.9496,0.0257,0.0114,0.0088</t>
+  </si>
+  <si>
+    <t>0.1913,0.0113,0.8306,0.0129</t>
+  </si>
+  <si>
+    <t>0.9062,0.1291,0.0067,0.0011</t>
+  </si>
+  <si>
+    <t>0.0044,0.9881,0.1054,0.0007</t>
+  </si>
+  <si>
+    <t>0.0428,0.9135,0.0578,0.0041</t>
+  </si>
+  <si>
+    <t>0.1171,0.0069,0.6896,0.1158</t>
+  </si>
+  <si>
+    <t>0.0105,0.0087,0.9839,0.0011</t>
+  </si>
+  <si>
+    <t>0.1011,0.0060,0.9175,0.0067</t>
+  </si>
+  <si>
+    <t>0.0169,0.0444,0.9618,0.0082</t>
+  </si>
+  <si>
+    <t>0.0042,0.9886,0.0113,0.0002</t>
+  </si>
+  <si>
+    <t>0.0394,0.0062,0.9631,0.0025</t>
+  </si>
+  <si>
+    <t>0.0078,0.6354,0.0040,0.9193</t>
+  </si>
+  <si>
+    <t>0.0160,0.9733,0.0583,0.0049</t>
+  </si>
+  <si>
+    <t>0.0041,0.9791,0.1798,0.0048</t>
+  </si>
+  <si>
+    <t>0.0016,0.9956,0.0039,0.0009</t>
+  </si>
+  <si>
+    <t>0.0085,0.0091,0.9828,0.0056</t>
+  </si>
+  <si>
+    <t>0.0127,0.0753,0.9662,0.0030</t>
+  </si>
+  <si>
+    <t>0.0032,0.0015,0.9942,0.0006</t>
+  </si>
+  <si>
+    <t>0.0060,0.0005,0.9944,0.0007</t>
+  </si>
+  <si>
+    <t>0.0029,0.0059,0.9933,0.0025</t>
+  </si>
+  <si>
+    <t>0.0039,0.0220,0.9880,0.0004</t>
+  </si>
+  <si>
+    <t>0.9890,0.0135,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9758,0.0011,0.0128,0.0051</t>
+  </si>
+  <si>
+    <t>0.9809,0.0041,0.0047,0.0078</t>
+  </si>
+  <si>
+    <t>0.0041,0.0102,0.9910,0.0090</t>
+  </si>
+  <si>
+    <t>0.9974,0.0010,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9877,0.0037,0.0051,0.0011</t>
+  </si>
+  <si>
+    <t>0.9807,0.0128,0.0065,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.8799,0.9965,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0149,0.9987,0.0006</t>
+  </si>
+  <si>
+    <t>0.0054,0.0050,0.9836,0.0097</t>
+  </si>
+  <si>
+    <t>0.0002,0.9106,0.9945,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.0046,0.9963,0.0007</t>
+  </si>
+  <si>
+    <t>0.0800,0.9186,0.0068,0.0002</t>
+  </si>
+  <si>
+    <t>0.0031,0.9920,0.0027,0.0003</t>
+  </si>
+  <si>
+    <t>0.9375,0.0074,0.0720,0.0047</t>
+  </si>
+  <si>
+    <t>0.2296,0.0702,0.8282,0.0133</t>
+  </si>
+  <si>
+    <t>0.0011,0.0031,0.9970,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.9632,0.9524,0.0003</t>
+  </si>
+  <si>
+    <t>0.0046,0.2859,0.9255,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9974,0.7771,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9838,0.9720,0.0001</t>
+  </si>
+  <si>
+    <t>0.0060,0.0009,0.1145,0.9488</t>
+  </si>
+  <si>
+    <t>0.0021,0.0025,0.0018,0.9977</t>
+  </si>
+  <si>
+    <t>0.0050,0.0010,0.0005,0.9977</t>
+  </si>
+  <si>
+    <t>0.0242,0.0021,0.0111,0.9825</t>
+  </si>
+  <si>
+    <t>0.0790,0.0012,0.0052,0.9595</t>
+  </si>
+  <si>
+    <t>0.0044,0.0016,0.0025,0.9963</t>
+  </si>
+  <si>
+    <t>0.0013,0.9773,0.5641,0.0002</t>
+  </si>
+  <si>
+    <t>0.0047,0.5981,0.9676,0.0021</t>
+  </si>
+  <si>
+    <t>0.0019,0.9334,0.8876,0.0017</t>
+  </si>
+  <si>
+    <t>0.0004,0.8883,0.9871,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9568,0.9921,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9559,0.8224,0.0003</t>
+  </si>
+  <si>
+    <t>0.9978,0.0007,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9870,0.0158,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9807,0.0123,0.0057,0.0009</t>
+  </si>
+  <si>
+    <t>0.9786,0.0048,0.0029,0.0075</t>
+  </si>
+  <si>
+    <t>0.9935,0.0033,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9885,0.0041,0.0009,0.0024</t>
+  </si>
+  <si>
+    <t>0.9911,0.0069,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9879,0.0051,0.0049,0.0008</t>
+  </si>
+  <si>
+    <t>0.9928,0.0013,0.0039,0.0007</t>
+  </si>
+  <si>
+    <t>0.9964,0.0010,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9953,0.0006,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9962,0.0004,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.9922,0.0011,0.0024,0.0016</t>
+  </si>
+  <si>
+    <t>0.9939,0.0016,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.9895,0.0056,0.0021,0.0013</t>
+  </si>
+  <si>
+    <t>0.0019,0.0029,0.9936,0.0050</t>
+  </si>
+  <si>
+    <t>0.0061,0.0052,0.9844,0.0032</t>
+  </si>
+  <si>
+    <t>0.9611,0.0035,0.0375,0.0015</t>
+  </si>
+  <si>
+    <t>0.1407,0.0008,0.9414,0.0003</t>
+  </si>
+  <si>
+    <t>0.0028,0.9952,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.0067,0.9914,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.1374,0.8642,0.0298,0.0072</t>
+  </si>
+  <si>
+    <t>0.1002,0.8992,0.0090,0.0045</t>
+  </si>
+  <si>
+    <t>0.0978,0.9338,0.0036,0.0006</t>
+  </si>
+  <si>
+    <t>0.0053,0.9932,0.0023,0.0002</t>
+  </si>
+  <si>
+    <t>0.8085,0.2986,0.0073,0.0013</t>
+  </si>
+  <si>
+    <t>0.8398,0.0540,0.0816,0.0295</t>
+  </si>
+  <si>
+    <t>0.6101,0.0033,0.5816,0.0029</t>
+  </si>
+  <si>
+    <t>0.8524,0.0230,0.1313,0.0057</t>
+  </si>
+  <si>
+    <t>0.6048,0.0422,0.4336,0.0152</t>
+  </si>
+  <si>
+    <t>0.0624,0.2511,0.0636,0.8191</t>
+  </si>
+  <si>
+    <t>0.0022,0.9936,0.0129,0.0007</t>
+  </si>
+  <si>
+    <t>0.0385,0.9414,0.0242,0.0147</t>
+  </si>
+  <si>
+    <t>0.0002,0.9952,0.0086,0.0196</t>
+  </si>
+  <si>
+    <t>0.0002,0.9228,0.9864,0.0003</t>
+  </si>
+  <si>
+    <t>0.0134,0.9862,0.0091,0.0001</t>
+  </si>
+  <si>
+    <t>0.7974,0.2747,0.0115,0.0038</t>
+  </si>
+  <si>
+    <t>0.9426,0.0576,0.0092,0.0019</t>
+  </si>
+  <si>
+    <t>0.9952,0.0012,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9815,0.0022,0.0191,0.0008</t>
+  </si>
+  <si>
+    <t>0.9924,0.0011,0.0020,0.0021</t>
+  </si>
+  <si>
+    <t>0.9644,0.0023,0.0383,0.0026</t>
+  </si>
+  <si>
+    <t>0.9945,0.0007,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9943,0.0009,0.0017,0.0009</t>
+  </si>
+  <si>
+    <t>0.9856,0.0008,0.0193,0.0004</t>
+  </si>
+  <si>
+    <t>0.9860,0.0020,0.0097,0.0017</t>
+  </si>
+  <si>
+    <t>0.0039,0.8266,0.7659,0.0002</t>
+  </si>
+  <si>
+    <t>0.0068,0.4844,0.9255,0.0009</t>
+  </si>
+  <si>
+    <t>0.0015,0.0266,0.9931,0.0004</t>
+  </si>
+  <si>
+    <t>0.1525,0.0050,0.9004,0.0048</t>
+  </si>
+  <si>
+    <t>0.9764,0.0016,0.0137,0.0025</t>
+  </si>
+  <si>
+    <t>0.8164,0.0104,0.2310,0.0062</t>
+  </si>
+  <si>
+    <t>0.0942,0.0162,0.9150,0.0165</t>
+  </si>
+  <si>
+    <t>0.9283,0.0266,0.0236,0.0043</t>
+  </si>
+  <si>
+    <t>0.1161,0.0006,0.0033,0.9520</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.0010,0.9994</t>
+  </si>
+  <si>
+    <t>0.0014,0.0088,0.0074,0.9946</t>
+  </si>
+  <si>
+    <t>0.0088,0.0005,0.0031,0.9943</t>
+  </si>
+  <si>
+    <t>0.0015,0.8966,0.9564,0.0019</t>
+  </si>
+  <si>
+    <t>0.9878,0.0039,0.0045,0.0010</t>
+  </si>
+  <si>
+    <t>0.1949,0.8131,0.0017,0.0138</t>
+  </si>
+  <si>
+    <t>0.9771,0.0035,0.0180,0.0020</t>
+  </si>
+  <si>
+    <t>0.6859,0.4207,0.0068,0.0020</t>
+  </si>
+  <si>
+    <t>0.9906,0.0008,0.0046,0.0019</t>
+  </si>
+  <si>
+    <t>0.8500,0.0116,0.0131,0.1773</t>
+  </si>
+  <si>
+    <t>0.9924,0.0012,0.0019,0.0016</t>
+  </si>
+  <si>
+    <t>0.0003,0.1846,0.9940,0.0050</t>
+  </si>
+  <si>
+    <t>0.9613,0.0016,0.0033,0.0322</t>
+  </si>
+  <si>
+    <t>0.9706,0.0025,0.0086,0.0145</t>
+  </si>
+  <si>
+    <t>0.9306,0.0898,0.0023,0.0014</t>
+  </si>
+  <si>
+    <t>0.9746,0.0052,0.0086,0.0046</t>
+  </si>
+  <si>
+    <t>0.9135,0.0178,0.0746,0.0051</t>
+  </si>
+  <si>
+    <t>0.1089,0.8095,0.0496,0.0180</t>
+  </si>
+  <si>
+    <t>0.9034,0.0233,0.1018,0.0012</t>
+  </si>
+  <si>
+    <t>0.7704,0.3100,0.0112,0.0067</t>
+  </si>
+  <si>
+    <t>0.9894,0.0012,0.0024,0.0047</t>
+  </si>
+  <si>
+    <t>0.9925,0.0012,0.0006,0.0033</t>
+  </si>
+  <si>
+    <t>0.9900,0.0021,0.0029,0.0020</t>
+  </si>
+  <si>
+    <t>0.9922,0.0004,0.0006,0.0054</t>
+  </si>
+  <si>
+    <t>0.9862,0.0015,0.0083,0.0020</t>
+  </si>
+  <si>
+    <t>0.9861,0.0021,0.0131,0.0007</t>
+  </si>
+  <si>
+    <t>0.9882,0.0037,0.0029,0.0030</t>
+  </si>
+  <si>
+    <t>0.9933,0.0009,0.0029,0.0008</t>
+  </si>
+  <si>
+    <t>0.8184,0.2379,0.0168,0.0088</t>
+  </si>
+  <si>
+    <t>0.6517,0.4738,0.0143,0.0028</t>
+  </si>
+  <si>
+    <t>0.5706,0.6410,0.0034,0.0008</t>
+  </si>
+  <si>
+    <t>0.8952,0.0426,0.0805,0.0020</t>
+  </si>
+  <si>
+    <t>0.9571,0.0545,0.0024,0.0018</t>
+  </si>
+  <si>
+    <t>0.9520,0.0181,0.0307,0.0050</t>
+  </si>
+  <si>
+    <t>0.9905,0.0032,0.0017,0.0010</t>
+  </si>
+  <si>
+    <t>0.9246,0.0857,0.0119,0.0039</t>
+  </si>
+  <si>
+    <t>0.0007,0.0055,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.8570,0.0823,0.0712,0.0072</t>
+  </si>
+  <si>
+    <t>0.0031,0.0035,0.9945,0.0014</t>
+  </si>
+  <si>
+    <t>0.0180,0.0041,0.9864,0.0013</t>
+  </si>
+  <si>
+    <t>0.1074,0.0024,0.9566,0.0004</t>
+  </si>
+  <si>
+    <t>0.0520,0.0295,0.9407,0.0058</t>
+  </si>
+  <si>
+    <t>0.0054,0.0063,0.9880,0.0035</t>
+  </si>
+  <si>
+    <t>0.0040,0.0005,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.0041,0.9939,0.0012</t>
+  </si>
+  <si>
+    <t>0.6977,0.0101,0.4365,0.0046</t>
+  </si>
+  <si>
+    <t>0.3301,0.0110,0.7901,0.0021</t>
+  </si>
+  <si>
+    <t>0.1520,0.0438,0.8576,0.0034</t>
+  </si>
+  <si>
+    <t>0.2753,0.2757,0.3615,0.0030</t>
+  </si>
+  <si>
+    <t>0.6883,0.0682,0.2928,0.0043</t>
+  </si>
+  <si>
+    <t>0.8415,0.0418,0.1072,0.0044</t>
+  </si>
+  <si>
+    <t>0.6900,0.0636,0.2393,0.0311</t>
+  </si>
+  <si>
+    <t>0.1478,0.0407,0.8183,0.0092</t>
+  </si>
+  <si>
+    <t>0.3725,0.7055,0.0190,0.0086</t>
+  </si>
+  <si>
+    <t>0.0221,0.9801,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9022,0.1859,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.9575,0.0658,0.0018,0.0011</t>
+  </si>
+  <si>
+    <t>0.9241,0.1268,0.0051,0.0009</t>
+  </si>
+  <si>
+    <t>0.8346,0.0315,0.1361,0.0041</t>
+  </si>
+  <si>
+    <t>0.9007,0.0056,0.1245,0.0042</t>
+  </si>
+  <si>
+    <t>0.9204,0.0107,0.0443,0.0195</t>
+  </si>
+  <si>
+    <t>0.8770,0.0179,0.1256,0.0062</t>
+  </si>
+  <si>
+    <t>0.6845,0.0045,0.2358,0.0514</t>
+  </si>
+  <si>
+    <t>0.0121,0.0163,0.9621,0.0228</t>
+  </si>
+  <si>
+    <t>0.0059,0.0542,0.9699,0.0073</t>
+  </si>
+  <si>
+    <t>0.2048,0.0284,0.8319,0.0110</t>
+  </si>
+  <si>
+    <t>0.2480,0.0713,0.6532,0.0086</t>
+  </si>
+  <si>
+    <t>0.0077,0.5237,0.8780,0.0006</t>
+  </si>
+  <si>
+    <t>0.9936,0.0016,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.9927,0.0027,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.9746,0.0041,0.0104,0.0056</t>
+  </si>
+  <si>
+    <t>0.9633,0.0379,0.0069,0.0021</t>
+  </si>
+  <si>
+    <t>0.9834,0.0126,0.0010,0.0021</t>
+  </si>
+  <si>
+    <t>0.9914,0.0042,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9913,0.0053,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9924,0.0015,0.0024,0.0014</t>
+  </si>
+  <si>
+    <t>0.0398,0.0132,0.9723,0.0017</t>
+  </si>
+  <si>
+    <t>0.5621,0.0788,0.4103,0.0531</t>
+  </si>
+  <si>
+    <t>0.3196,0.0094,0.5269,0.1355</t>
+  </si>
+  <si>
+    <t>0.0143,0.0145,0.9847,0.0019</t>
+  </si>
+  <si>
+    <t>0.0022,0.0066,0.9838,0.0243</t>
+  </si>
+  <si>
+    <t>0.0080,0.0152,0.9802,0.0089</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0186,0.0573,0.9607,0.0010</t>
+  </si>
+  <si>
+    <t>0.0024,0.0035,0.9956,0.0013</t>
+  </si>
+  <si>
+    <t>0.0097,0.0196,0.9724,0.0025</t>
+  </si>
+  <si>
+    <t>0.0431,0.0154,0.9321,0.0164</t>
+  </si>
+  <si>
+    <t>0.8593,0.0078,0.1774,0.0062</t>
+  </si>
+  <si>
+    <t>0.4940,0.0037,0.6673,0.0024</t>
+  </si>
+  <si>
+    <t>0.9703,0.0016,0.0090,0.0076</t>
+  </si>
+  <si>
+    <t>0.9917,0.0044,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9928,0.0025,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.9933,0.0020,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9752,0.0148,0.0086,0.0031</t>
+  </si>
+  <si>
+    <t>0.9976,0.0003,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9904,0.0048,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.9966,0.0016,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9959,0.0002,0.0001,0.0022</t>
+  </si>
+  <si>
+    <t>0.0137,0.0200,0.9628,0.0010</t>
+  </si>
+  <si>
+    <t>0.0010,0.0233,0.9922,0.0025</t>
+  </si>
+  <si>
+    <t>0.0031,0.0187,0.9900,0.0035</t>
+  </si>
+  <si>
+    <t>0.0213,0.0667,0.9300,0.0048</t>
+  </si>
+  <si>
+    <t>0.0018,0.0007,0.9967,0.0010</t>
+  </si>
+  <si>
+    <t>0.1100,0.0319,0.6931,0.1786</t>
+  </si>
+  <si>
+    <t>0.0411,0.0045,0.9622,0.0069</t>
+  </si>
+  <si>
+    <t>0.0020,0.0016,0.9943,0.0019</t>
+  </si>
+  <si>
+    <t>0.8747,0.0002,0.0006,0.2718</t>
+  </si>
+  <si>
+    <t>0.0493,0.0081,0.0014,0.9781</t>
+  </si>
+  <si>
+    <t>0.0469,0.0009,0.0036,0.9813</t>
+  </si>
+  <si>
+    <t>0.0012,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.0014,0.9987</t>
+  </si>
+  <si>
+    <t>0.8484,0.0099,0.0108,0.1643</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2222,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2264,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2281,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,10 +2348,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2379,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,10 +2390,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2432,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,10 +2544,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,10 +2586,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2642,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2810,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2936,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2995,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3107,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3412,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,10 +3482,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3496,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,10 +3510,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3597,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,10 +3636,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3667,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3860,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4003,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4112,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4378,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,10 +4462,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4532,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,10 +4574,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4591,7 @@
         <v>259</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4633,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4647,7 @@
         <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4703,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4840,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5039,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,10 +5050,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,10 +5078,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5386,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
